--- a/stories/arbres/ATOM-REL.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hanaé joue dans sa chambre. Maman plie des chaussettes près de la fenêtre. Hanaé a un train en bois. Les roues font un petit bruit. Flora arrive. Flora regarde le train. Hanaé serre le train un moment. Maman s'approche. Maman dit : tu peux prêter le train. Prêter, c'est laisser jouer Flora. Hanaé tend le train. Flora le prend. Flora fait rouler le train. Hanaé reste près de maman. Hanaé attend. C'est le tour de Flora. Puis c'est le tour d'Hanaé. Flora rend le train. Hanaé le fait rouler aussi. Maman dit : tu peux proposer un autre jeu. Hanaé prend les cubes. Hanaé dit : un autre jeu ? Flora sourit. Elles bâtissent une petite gare. Le bois sent le sapin. Maman reste tout près. Hanaé a su prêter. Chacune a eu son tour. Elles ont un autre jeu.</t>
+          <t>Hanaé joue dans sa chambre. Maman plie des chaussettes près de la fenêtre. Hanaé a un train en bois. Les roues font un petit bruit. Flora arrive. Flora regarde le train. Hanaé serre le train un moment. Maman s'approche. Tu peux prêter le train. Prêter, c'est laisser jouer Flora. Hanaé tend le train. Flora le prend. Flora fait rouler le train. Hanaé reste près de maman. Hanaé attend. C'est le tour de Flora. Puis c'est le tour d'Hanaé. Flora rend le train. Hanaé le fait rouler aussi. Tu peux proposer un autre jeu. Hanaé prend les cubes. Un autre jeu ? Flora sourit. Elles bâtissent une petite gare. Le bois sent le sapin. Maman reste tout près. Hanaé a su prêter. Chacune a eu son tour. Elles ont un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hanaé joue dans sa chambre. Maman plie des chaussettes près de la fenêtre. Hanaé a un train en bois. Les roues font un petit bruit. Flora arrive. Flora regarde le train. Hanaé serre le train un moment. Maman s'approche.
+maman|Tu peux prêter le train. Prêter, c'est laisser jouer Flora.
+narrateur|Hanaé tend le train. Flora le prend. Flora fait rouler le train. Hanaé reste près de maman. Hanaé attend. C'est le tour de Flora. Puis c'est le tour d'Hanaé. Flora rend le train. Hanaé le fait rouler aussi.
+maman|Tu peux proposer un autre jeu.
+narrateur|Hanaé prend les cubes.
+enfant-f|Un autre jeu ?
+narrateur|Flora sourit. Elles bâtissent une petite gare. Le bois sent le sapin. Maman reste tout près. Hanaé a su prêter. Chacune a eu son tour. Elles ont un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hanaé a un train. Que peut-elle faire ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hanaé a prêté le train. Flora a eu son tour. Puis elles ont un autre jeu. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hanaé range un cube. Le train reste au calme. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Flora sourit. Elles bâtissent une petite gare. Le bois sent le sapin. Maman reste tout près. Hanaé a su prêter. Chacune a eu son tour. Elles ont un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Hanaé a un train. Que peut-elle faire ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Hanaé a prêté le train. Flora a eu son tour. Puis elles ont un autre jeu. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Hanaé range un cube. Le train reste au calme. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hanaé prête le train en bois</t>
+          <t>Le train en bois de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un carré de soleil dort sur le tapis. Sarah fait rouler son train en bois. Nina le voudrait. Sarah prête, attend son tour, puis propose les cubes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hanaé joue dans sa chambre. Maman plie des chaussettes près de la fenêtre. Hanaé a un train en bois. Les roues font un petit bruit. Flora arrive. Flora regarde le train. Hanaé serre le train un moment. Maman s'approche. Tu peux prêter le train. Prêter, c'est laisser jouer Flora. Hanaé tend le train. Flora le prend. Flora fait rouler le train. Hanaé reste près de maman. Hanaé attend. C'est le tour de Flora. Puis c'est le tour d'Hanaé. Flora rend le train. Hanaé le fait rouler aussi. Tu peux proposer un autre jeu. Hanaé prend les cubes. Un autre jeu ? Flora sourit. Elles bâtissent une petite gare. Le bois sent le sapin. Maman reste tout près. Hanaé a su prêter. Chacune a eu son tour. Elles ont un autre jeu.</t>
+          <t>Un carré de soleil dort sur le tapis. Il touche une chaussette pliée. Maman pose une pile douce près de la commode. Ça sent le bois du train. Un rayon glisse sur le wagon rouge. Cette chaussette est toute chaude, Sarah. Tu as vu le carré de soleil ? Oui, maman. Il est sur le tapis. Il est bien jaune, oui. En ce moment, Sarah pousse le train en bois. Les roues font un petit bruit. Toc, toc, toc, sur le tapis. Le wagon va à la gare. Doucement. Le tapis aime le train. Nina arrive près de la porte. Elle a les chaussons bleus. Elle regarde le train. Je peux, Sarah ? Sarah serre le train un moment. Tu peux prêter le train. Prêter, c'est laisser Nina jouer. Puis tu attends ton tour. Tu peux. C'est ton tour. Sarah tend le train. Nina le fait rouler. Les roues tapent plus loin. Sarah s'assoit près de maman. Elle attend. Elle compte les chaussettes pliées. Une. Deux. Trois. Tu attends ton tour. Bravo, Sarah. Le bois sent encore le sapin. Nina rend le train. C'est ton tour. Sarah fait rouler le wagon aussi. Le carré de soleil a un peu bougé. Puis Nina le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les cubes ? Oui. On fait une petite gare. Sarah prend les cubes. Nina pose un cube bleu. Elles bâtissent une gare basse. Vous avez prêté. Chacune a eu son tour. Puis un autre jeu. C'est du bon travail. La gare est solide ? Oui, maman. Le train se repose près des cubes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hanaé joue dans sa chambre. Maman plie des chaussettes près de la fenêtre. Hanaé a un train en bois. Les roues font un petit bruit. Flora arrive. Flora regarde le train. Hanaé serre le train un moment. Maman s'approche.
-maman|Tu peux prêter le train. Prêter, c'est laisser jouer Flora.
-narrateur|Hanaé tend le train. Flora le prend. Flora fait rouler le train. Hanaé reste près de maman. Hanaé attend. C'est le tour de Flora. Puis c'est le tour d'Hanaé. Flora rend le train. Hanaé le fait rouler aussi.
+          <t>narrateur|Un carré de soleil dort sur le tapis.
+narrateur|Il touche une chaussette pliée.
+narrateur|Maman pose une pile douce près de la commode.
+narrateur|Ça sent le bois du train.
+narrateur|Un rayon glisse sur le wagon rouge.
+maman|Cette chaussette est toute chaude, Sarah.
+maman|Tu as vu le carré de soleil ?
+enfant-f|Oui, maman.
+enfant-f|Il est sur le tapis.
+maman|Il est bien jaune, oui.
+narrateur|En ce moment, Sarah pousse le train en bois.
+narrateur|Les roues font un petit bruit.
+narrateur|Toc, toc, toc, sur le tapis.
+enfant-f|Le wagon va à la gare.
+maman|Doucement.
+maman|Le tapis aime le train.
+narrateur|Nina arrive près de la porte.
+narrateur|Elle a les chaussons bleus.
+narrateur|Elle regarde le train.
+enfant-f|Je peux, Sarah ?
+narrateur|Sarah serre le train un moment.
+maman|Tu peux prêter le train.
+maman|Prêter, c'est laisser Nina jouer.
+maman|Puis tu attends ton tour.
+enfant-f|Tu peux.
+enfant-f|C'est ton tour.
+narrateur|Sarah tend le train.
+narrateur|Nina le fait rouler.
+narrateur|Les roues tapent plus loin.
+narrateur|Sarah s'assoit près de maman.
+narrateur|Elle attend.
+narrateur|Elle compte les chaussettes pliées.
+enfant-f|Une.
+enfant-f|Deux.
+enfant-f|Trois.
+maman|Tu attends ton tour.
+maman|Bravo, Sarah.
+narrateur|Le bois sent encore le sapin.
+narrateur|Nina rend le train.
+enfant-f|C'est ton tour.
+narrateur|Sarah fait rouler le wagon aussi.
+narrateur|Le carré de soleil a un peu bougé.
+narrateur|Puis Nina le voudrait encore.
 maman|Tu peux proposer un autre jeu.
-narrateur|Hanaé prend les cubes.
-enfant-f|Un autre jeu ?
-narrateur|Flora sourit. Elles bâtissent une petite gare. Le bois sent le sapin. Maman reste tout près. Hanaé a su prêter. Chacune a eu son tour. Elles ont un autre jeu.</t>
+maman|Un autre jeu, c'est possible.
+enfant-f|Les cubes ?
+maman|Oui.
+maman|On fait une petite gare.
+narrateur|Sarah prend les cubes.
+narrateur|Nina pose un cube bleu.
+narrateur|Elles bâtissent une gare basse.
+maman|Vous avez prêté.
+maman|Chacune a eu son tour.
+maman|Puis un autre jeu.
+maman|C'est du bon travail.
+maman|La gare est solide ?
+enfant-f|Oui, maman.
+narrateur|Le train se repose près des cubes.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hanaé a un train. Que peut-elle faire ?</t>
+          <t>Sarah a un train. Que peut-elle faire ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hanaé a un train. Que peut-elle faire ?</t>
+          <t>narrateur|Sarah a un train.
+narrateur|Que peut-elle faire ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hanaé a prêté le train. Flora a eu son tour. Puis elles ont un autre jeu. Maman est là.</t>
+          <t>Sarah a prêté le train. Nina a eu son tour. Puis elles ont un autre jeu. Tu as prêté. Tu as attendu. Bravo, Sarah. C'est du bon travail. Le cube bleu est en bas ? Oui. La gare est basse. Un autre jeu, c'est bien aussi. Le tapis est chaud sous les genoux. Le carré de soleil a glissé un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1738,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hanaé a prêté le train. Flora a eu son tour. Puis elles ont un autre jeu. Maman est là.</t>
+          <t>narrateur|Sarah a prêté le train.
+narrateur|Nina a eu son tour.
+narrateur|Puis elles ont un autre jeu.
+maman|Tu as prêté.
+maman|Tu as attendu.
+maman|Bravo, Sarah.
+maman|C'est du bon travail.
+maman|Le cube bleu est en bas ?
+enfant-f|Oui.
+enfant-f|La gare est basse.
+maman|Un autre jeu, c'est bien aussi.
+narrateur|Le tapis est chaud sous les genoux.
+narrateur|Le carré de soleil a glissé un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hanaé range un cube. Le train reste au calme. Maman sourit.</t>
+          <t>Sarah range un cube dans la boîte. Le train reste au calme. On ferme la boîte ? Oui, maman. Donne-moi le wagon. Maman pose le train dans la caisse. Le bois tape un tout petit coup. Tes chaussettes attendent encore. On les met dans le tiroir ? Oui. Le tiroir glisse, tout doux. Merci d'avoir prêté.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1914,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hanaé range un cube. Le train reste au calme. Maman sourit.</t>
+          <t>narrateur|Sarah range un cube dans la boîte.
+narrateur|Le train reste au calme.
+maman|On ferme la boîte ?
+enfant-f|Oui, maman.
+maman|Donne-moi le wagon.
+narrateur|Maman pose le train dans la caisse.
+narrateur|Le bois tape un tout petit coup.
+maman|Tes chaussettes attendent encore.
+maman|On les met dans le tiroir ?
+enfant-f|Oui.
+narrateur|Le tiroir glisse, tout doux.
+maman|Merci d'avoir prêté.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1953,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai prêté le train. Puis les cubes. Bravo. Tu as fait du bon travail. Le carré de soleil est plus petit. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2093,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai prêté le train.
+enfant-f|Puis les cubes.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le carré de soleil est plus petit.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un carré de soleil dort sur le tapis. Il touche une chaussette pliée. Maman pose une pile douce près de la commode. Ça sent le bois du train. Un rayon glisse sur le wagon rouge. Cette chaussette est toute chaude, Sarah. Tu as vu le carré de soleil ? Oui, maman. Il est sur le tapis. Il est bien jaune, oui. En ce moment, Sarah pousse le train en bois. Les roues font un petit bruit. Toc, toc, toc, sur le tapis. Le wagon va à la gare. Doucement. Le tapis aime le train. Nina arrive près de la porte. Elle a les chaussons bleus. Elle regarde le train. Je peux, Sarah ? Sarah serre le train un moment. Tu peux prêter le train. Prêter, c'est laisser Nina jouer. Puis tu attends ton tour. Tu peux. C'est ton tour. Sarah tend le train. Nina le fait rouler. Les roues tapent plus loin. Sarah s'assoit près de maman. Elle attend. Elle compte les chaussettes pliées. Une. Deux. Trois. Tu attends ton tour. Bravo, Sarah. Le bois sent encore le sapin. Nina rend le train. C'est ton tour. Sarah fait rouler le wagon aussi. Le carré de soleil a un peu bougé. Puis Nina le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les cubes ? Oui. On fait une petite gare. Sarah prend les cubes. Nina pose un cube bleu. Elles bâtissent une gare basse. Vous avez prêté. Chacune a eu son tour. Puis un autre jeu. C'est du bon travail. La gare est solide ? Oui, maman. Le train se repose près des cubes.</t>
+          <t>Un carré de soleil dort sur le tapis. Il touche une chaussette pliée. Maman pose une pile douce près de la commode. Ça sent le bois du train. Un rayon glisse sur le wagon rouge. Cette chaussette est toute chaude, Sarah. Tu as vu le carré de soleil ? Oui, maman. Il est sur le tapis. Il est bien jaune, oui. En ce moment, Sarah pousse le train en bois. Les roues font un petit bruit. Toc, toc, toc, sur le tapis. Le wagon va à la gare. Doucement. Le tapis aime le train. Nina arrive près de la porte. Elle a les chaussons bleus. Elle regarde le train. Je peux, Sarah ? Sarah serre le train un moment. Tu peux prêter le train. Prêter, c'est laisser Nina jouer. Puis tu attends ton tour. Tu peux. C'est ton tour. Sarah tend le train. Nina le fait rouler. Les roues tapent plus loin. Sarah s'assoit près de maman. Elle attend. Elle compte les chaussettes pliées. Une. Deux. Trois. Tu attends ton tour. Bravo, Sarah. Le bois sent encore le sapin. Nina rend le train. C'est ton tour. Sarah fait rouler le wagon aussi. Le carré de soleil a un peu bougé. Puis Nina le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les cubes ? Oui. On fait une petite gare. Sarah prend les cubes. Nina pose un cube bleu. Elles bâtissent une gare basse. Vous avez prêté. Chacune a eu son tour. Puis un autre jeu. La gare est solide ? Oui, maman. Le train se repose près des cubes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hanaé joue dans sa chambre. Maman plie des chaussettes près de la fenêtre. Hanaé a un train en bois. Les roues font un petit bruit. Flora arrive. Flora regarde le train. Hanaé serre le train un moment. Maman s'approche. Maman dit : tu peux &lt;emphasis level="moderate"&gt;prêter&lt;/emphasis&gt; le train. Prêter, c'est laisser jouer Flora. Hanaé tend le train. Flora le prend. Flora fait rouler le train. Hanaé reste près de maman. Hanaé attend. C'est le tour de Flora. Puis c'est le tour d'Hanaé. Flora rend le train. Hanaé le fait rouler aussi. Maman dit : tu peux proposer un autre jeu. Hanaé prend les cubes. Hanaé dit : un autre jeu ? Flora sourit. Elles bâtissent une petite gare. Le bois sent le sapin. Maman reste tout près. Hanaé a su prêter. Chacune a eu son tour. Elles ont un autre jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un carré de soleil dort sur le tapis. Il touche une chaussette pliée. Maman pose une pile douce près de la commode. Ça sent le bois du train. Un rayon glisse sur le wagon rouge. Cette chaussette est toute chaude, Sarah. Tu as vu le carré de soleil ? Oui, maman. Il est sur le tapis. Il est bien jaune, oui. En ce moment, Sarah pousse le train en bois. Les roues font un petit bruit. Toc, toc, toc, sur le tapis. Le wagon va à la gare. Doucement. Le tapis aime le train. Nina arrive près de la porte. Elle a les chaussons bleus. Elle regarde le train. Je peux, Sarah ? Sarah serre le train un moment. Tu peux prêter le train. Prêter, c'est laisser Nina jouer. Puis tu attends ton tour. Tu peux. C'est ton tour. Sarah tend le train. Nina le fait rouler. Les roues tapent plus loin. Sarah s'assoit près de maman. Elle attend. Elle compte les chaussettes pliées. Une. Deux. Trois. Tu attends ton tour. Bravo, Sarah. Le bois sent encore le sapin. Nina rend le train. C'est ton tour. Sarah fait rouler le wagon aussi. Le carré de soleil a un peu bougé. Puis Nina le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les cubes ? Oui. On fait une petite gare. Sarah prend les cubes. Nina pose un cube bleu. Elles bâtissent une gare basse. Vous avez prêté. Chacune a eu son tour. Puis un autre jeu. La gare est solide ? Oui, maman. Le train se repose près des cubes.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1378,13 +1378,11 @@
 maman|Vous avez prêté.
 maman|Chacune a eu son tour.
 maman|Puis un autre jeu.
-maman|C'est du bon travail.
 maman|La gare est solide ?
 enfant-f|Oui, maman.
 narrateur|Le train se repose près des cubes.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hanaé a un train. Que peut-elle faire ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a un train. Que peut-elle faire ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1567,6 @@
 narrateur|Que peut-elle faire ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a prêté le train. Nina a eu son tour. Puis elles ont un autre jeu. Tu as prêté. Tu as attendu. Bravo, Sarah. C'est du bon travail. Le cube bleu est en bas ? Oui. La gare est basse. Un autre jeu, c'est bien aussi. Le tapis est chaud sous les genoux. Le carré de soleil a glissé un peu.</t>
+          <t>Sarah a prêté le train. Nina a eu son tour. Puis elles ont un autre jeu. Tu as prêté. Tu as attendu. Bravo, Sarah. Le cube bleu est en bas ? Oui. La gare est basse. Un autre jeu, c'est bien aussi. Le tapis est chaud sous les genoux. Le carré de soleil a glissé un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hanaé a prêté le train. Flora a eu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Puis elles ont un autre jeu. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a prêté le train. Nina a eu son tour. Puis elles ont un autre jeu. Tu as prêté. Tu as attendu. Bravo, Sarah. Le cube bleu est en bas ? Oui. La gare est basse. Un autre jeu, c'est bien aussi. Le tapis est chaud sous les genoux. Le carré de soleil a glissé un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1744,7 +1741,6 @@
 maman|Tu as prêté.
 maman|Tu as attendu.
 maman|Bravo, Sarah.
-maman|C'est du bon travail.
 maman|Le cube bleu est en bas ?
 enfant-f|Oui.
 enfant-f|La gare est basse.
@@ -1753,7 +1749,6 @@
 narrateur|Le carré de soleil a glissé un peu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hanaé range un cube. Le train reste au calme. Maman sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah range un cube dans la boîte. Le train reste au calme. On ferme la boîte ? Oui, maman. Donne-moi le wagon. Maman pose le train dans la caisse. Le bois tape un tout petit coup. Tes chaussettes attendent encore. On les met dans le tiroir ? Oui. Le tiroir glisse, tout doux. Merci d'avoir prêté.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1928,7 +1923,6 @@
 maman|Merci d'avoir prêté.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai prêté le train. Puis les cubes. Bravo. Tu as fait du bon travail. Le carré de soleil est plus petit. L'histoire est finie.</t>
+          <t>J'ai prêté le train. Puis les cubes. Bravo. Le carré de soleil est plus petit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai prêté le train. Puis les cubes. Bravo. Le carré de soleil est plus petit.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,12 +2090,9 @@
           <t>enfant-f|J'ai prêté le train.
 enfant-f|Puis les cubes.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le carré de soleil est plus petit.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le carré de soleil est plus petit.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2120,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hanaé, Flora, maman</t>
+          <t>Sarah, Nina, maman</t>
         </is>
       </c>
     </row>
